--- a/data/excel/organization.xlsx
+++ b/data/excel/organization.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,6 +663,107 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>中华苏维埃共和国</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1931年11月7日</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>土地革命战争时期中国共产党领导建立的全国性红色政权，首都设于江西瑞金。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>中华全国总工会</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>全总</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1925年5月1日</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>中国共产党领导的全国工人阶级的群众组织，1925 年第二次全国劳动大会上成立。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>中国人民志愿军</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>志愿军</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1950年10月</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>抗美援朝战争中中国人民组成的志愿部队，赴朝与朝鲜人民军并肩作战。</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/excel/organization.xlsx
+++ b/data/excel/organization.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -761,6 +761,5345 @@
         </is>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>中共中央政治局</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>中央政治局</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1927年5月</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>中国共产党中央委员会的政治领导机构，在中央委员会全体会议闭会期间行使中央委员会职权。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>中共中央书记处</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>中央书记处</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1934年1月</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>中央政治局及其常务委员会的办事机构。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>中共中央军事委员会</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>中央军委</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>中国共产党领导人民武装力量的最高军事领导机关。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>中共中央纪律检查委员会</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>中央纪委</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1978年12月</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>党的最高纪律检查机关，由中央委员会全体会议选举产生。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>中共中央办公厅</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>中办</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1948年</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>中共中央的综合办事机构。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>中共中央宣传部</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>中宣部</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1924年</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>中共中央主管宣传思想工作的职能部门。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>中共中央组织部</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中组部</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>中共中央主管干部与党的组织工作的职能部门。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>中共中央统一战线工作部</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中央统战部</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1944年</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>中共中央主管统一战线工作的职能部门。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>中华苏维埃共和国临时中央政府</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>临时中央政府</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1931年11月7日</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>中华苏维埃第一次全国代表大会在江西瑞金选举产生的中央工农民主政府。</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>中央人民政府委员会</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1949年9月30日</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议第一届全体会议选举产生的新中国最高国家政权机关。</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>中华人民共和国国务院</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>国务院</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1954年9月</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>中华人民共和国中央人民政府，最高国家权力机关的执行机关和最高国家行政机关。</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>全国人民代表大会</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>全国人大</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1954年9月</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>中华人民共和国最高国家权力机关。</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>人民政协/政协</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1949年9月</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>中国人民爱国统一战线的组织，中国共产党领导的多党合作和政治协商的重要机构。</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>中国工农红军第四军</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>红四军</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1928年4月</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>井冈山会师后由南昌起义余部与秋收起义部队合编而成的人民军队。</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>中国工农红军第一方面军</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>红一方面军/中央红军</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1930年8月</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>由红一军团和红三军团合编组成，是中央苏区的主力红军。</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>中国工农红军第二方面军</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>红二方面军</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1936年7月</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>由红二军团、红六军团和红三十二军组成。</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>中国工农红军第四方面军</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>红四方面军</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1931年11月</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>鄂豫皖苏区的主力红军，后转战川陕。</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>东北抗日联军</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>抗联</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1936年</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>中国共产党领导的东北抗日武装，在极端艰苦条件下坚持抗战十四年。</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>八路军第一一五师</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>一一五师</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1937年8月</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>八路军主力师之一，平型关大捷的作战部队。</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>中国工农红军第二十五军</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>红二十五军</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1931年10月</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>鄂豫皖苏区组建的红军部队，长征中最先到达陕北。</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>中国人民解放军第四野战军</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>四野</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1949年3月</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>解放战争时期人民解放军五大野战军之一，参与辽沈、平津战役。</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>中国人民解放军第三野战军</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>三野</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1949年2月</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>解放战争时期人民解放军五大野战军之一，参与淮海、渡江战役。</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>中国人民解放军第二野战军</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>二野</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1949年2月</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>解放战争时期人民解放军五大野战军之一，由晋冀鲁豫野战军发展而来。</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>中国人民解放军第一野战军</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>一野</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1949年2月</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>解放战争时期人民解放军五大野战军之一，由西北野战军发展而来。</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>中华全国妇女联合会</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>全国妇联</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1949年3月</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>中国共产党领导的全国各族各界妇女的群众组织。</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>中华全国青年联合会</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>全国青联</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1949年5月</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>中国共产党领导的全国各族各界青年的群众组织。</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>中国少年先锋队</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>少先队</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1949年10月13日</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>中国共产党委托中国共产主义青年团领导的中国少年儿童的群众组织。</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>共产国际</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>第三国际</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1919年3月</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1919 年成立的国际共产主义组织，曾对中国共产党的创建与早期活动给予帮助。</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>中国国民党</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>国民党</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1919年10月</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>政党</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>由孙中山改组成立的政党，曾两度与中国共产党合作。</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>中国民主同盟</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>民盟</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1941年3月</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>政党</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>中国的民主党派之一，由文教界知识分子为主组成。</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>中国国民党革命委员会</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>民革</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1948年1月</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>政党</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>中国的民主党派之一，由原中国国民党民主派人士组成。</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>三五九旅</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>为克服经济上的严重困难，中共中央在延安召开生产动员大会，毛泽东发出“自己动手”的号召</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>上海市人民政府</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>国务院批转上海市人民政府、国务院改造振兴上海调研组《关于上海经济发展战略的汇报提纲》，并发出通知指出，改造、振兴上海是关系我国四化建设的大事</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434796/index.html</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>世界银行</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>中国恢复在世界银行的代表权</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>中共中央党校</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>毛泽东在中共中央党校作题为《反对投降主义》的讲话</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434793/index.html</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>中共中央北方局</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>中共中央北方局在太原组建新的领导机关</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>中共中央政治局常委会</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>中共中央政治局常委会召开会议，专门听取全国人大常委会、国务院、全国政协、最高人民法院、最高人民检察院党组工作汇报</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>中共中央统战部</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>陈云在中共中央统战部讨论工商联工作会议上作总结讲话</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434654/index.html</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>中华人民共和国中央人民政府</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议第一届全体会议在北平举行</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>中华人民共和国中央军事委员会</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>国务院、中央军委发布公告：中国人民解放军驻香港特别行政区部队组建完成</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434845/index.html</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>中华人民共和国全国人民代表大会</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>《中华人民共和国全国人民代表大会及地方各级人民代表大会选举法》公布施行</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>中华人民共和国政府</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>中缅两国签订《中华人民共和国政府和缅甸联邦政府关于两国边界问题的协定》、《中华人民共和国和缅甸联邦之间的友好和互不侵犯条约》</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>中华全国供销合作总社</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>中华全国合作社第一次代表大会在北京举行</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434654/index.html</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>中华全国学生联合会</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>中华全国学生联合会在北平宣布成立</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434758/index.html</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>中华全国工商业联合会</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>第一届中华全国工商业联合会会员代表大会开幕</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434565/index.html</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>中原军区</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>毛泽东、朱德发布《向全国进军的命令》</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>中国人民大学</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>刘少奇签发中共中央关于成立中国人民大学的决定</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434840/index.html</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>中国人民解放军总部</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>中国人民解放军总部发表宣言，提出“打倒蒋介石，解放全中国”的口号</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>中国人民解放军海军</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>根据联合国安理会有关决议，中国人民解放军海军首批舰艇编队赴亚丁湾、索马里海域执行护航任务</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>中国人民解放军空军</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>中国人民解放军空军领导机构成立</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>中国人民银行</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>中国人民银行成立并发行人民币</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>中国共产党中央委员会</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>中央政治局扩大会议召开</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>中国工会</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>中国工会第七次全国代表大会在北京举行</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434697/index.html</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>中国工程院</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>习近平在中国科学院第二十次院士大会、中国工程院第十五次院士大会、中国科协第十次全国代表大会上讲话指出，要加快建设科技强国，实现高水平科技自立自强</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>中国新民主主义青年团</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>中国新民主主义青年团第一次全国代表大会在北平召开</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434737/index.html</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>中国社会主义青年团</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>中国社会主义青年团第一次全国代表大会在广州召开，中国社会主义青年团成立</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>中国科学技术协会</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>中国科学技术协会第四次全国代表大会在北京举行</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434718/index.html</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>中国科学院</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>中共中央发出《关于召开全国科学大会的通知》，要求抓紧落实党的知识分子政策，迅速恢复被撤掉的科研机构，恢复科研人员的技术职称，建立考核制度，实行技术岗位责任制</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>中国空军</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>中国政府宣布划设东海防空识别区，并发布航空器识别规则公告和识别区示意图</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>中央人民政府</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议第一届全体会议在北平举行</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>中央人民政府政务院</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>中华人民共和国中央人民政府成立</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>中央党校</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>中央党校内部刊物《理论动态》刊登《实践是检验真理的唯一标准》一文</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>中央军事委员会</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>中共七届一中全会选举毛泽东、朱德、刘少奇、周恩来、任弼时为中央书记处书记，毛泽东为中央委员会主席、中央政治局主席、中央书记处主席</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>中央宣传部</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>中央政治局召开会议</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>中央政治局常委会</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>中央政治局常委会会议专题研究新疆稳定工作</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>中央政法委员会</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>中共中央发出《关于成立中央政法委员会的通知》</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434841/index.html</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>中央民族学院</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>政务院第六十次政务会议批准《培养少数民族干部试行方案》和《筹办中央民族学院试行方案》</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>中央纪律检查委员会</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>中共中央决定成立中央及各级党的纪律检查委员会，朱德兼任中央纪律检查委员会书记</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>中央组织部</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>中共中央办公厅转发中央组织部、中央宣传部《关于在党的基层组织和党员中深入开展创先争优活动的意见》，对开展创先争优活动作出部署</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>中央美术学院</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>习近平主持召开中央全面深化改革领导小组第二十七次会议强调，当前和今后一个时期，是全面深化改革的施工高峰期，是落实改革任务的攻坚期，抓谋划、抓统筹、抓落实的任务依然艰巨繁重</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434469/434633/index.html</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>中央银行</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>国务院作出《关于金融体制改革的决定》</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>中央革命军事委员会</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>在以周恩来为书记的中共中央前敌委员会领导下，贺龙、叶挺、朱德、刘伯承等率领党所掌握和影响的军队两万余人，在江西南昌打响武装反抗国民党反动派的第一枪</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>中央顾问委员会</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>中国共产党第十二次全国代表大会举行</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>中开新局</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>习近平在中央党校(国家行政学院)中青年干部培训班开班式上发表讲话强调，历史总是在不断解决问题中前进的</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434552/index.html</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>九届全国人大</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>九届全国人大一次会议举行</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>九届全国人大常委会</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>六届全国人大二次会议通过《中华人民共和国民族区域自治法》</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>人民公社</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>中共中央发出《关于农村人民公社当前政策问题的紧急指示信》，要求坚决纠正农村人民公社的“共产风”</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>人民日报社</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>由《晋察冀日报》和晋冀鲁豫《人民日报》合并而成的中共华北局机关报《人民日报》在河北省平山县里庄创刊，毛泽东为《人民日报》题写报头</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434680/index.html</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>人民法院</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>中共中央发出通知，根据五届人大一次会议通过的宪法，重新设置人民检察院，与公安机关、人民法院互相配合，又相互制约，同各种违法乱纪行为作斗争</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434719/index.html</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>人民解放军</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>中华人民共和国中央人民政府成立</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>人民解放军总部</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>中央政治局会议在陕北清涧枣林沟召开，讨论中央机关行动问题</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>侵华日军</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>日本代表在投降书上签字</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>党和政府</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>上旬　应朝鲜党和政府的请求，中共中央作出抗美援朝、保家卫国的战略决策</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>全国人大常委会</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>一届全国人大一次会议举行</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>全国人民代表大会常务委员会</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>邓小平在全国政协讨论五届全国人大常委会五次会议通过的《全国人民代表大会常务委员会告台湾同胞书》的座谈会上讲话，提出把解决台湾问题、完成祖国统一大业提上具体日程</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434818/index.html</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>全国工会</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>朱德在全国工会工作会议开幕式上讲话</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434657/index.html</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>全国总工会</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>全国总工会、共青团中央等九单位联合向全国人民特别是青少年发出倡议，开展以讲文明、讲礼貌、讲卫生、讲秩序、讲道德和心灵美、语言美、行为美、环境美为主要内容的“五讲四美”文明礼貌活动</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>八国集团</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2007年6月8日 胡锦涛在八国集团同发展中国家领导人对话会议上讲话，提出中国对气候变化问题的原则立场</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434673/index.html</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>八届全国人大</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>八届全国人大一次会议举行</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>八届全国人大常委会</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>八届全国人大常委会第八次会议通过《中华人民共和国劳动法》</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>八路军总部</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>八路军第一二九师主力同冀南军区部队一起进行反“扫荡”作战，巩固了冀南抗日根据地</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>内蒙古自治区人民政府</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>《中华人民共和国民族区域自治实施纲要》公布施行，对民族自治地方的建立、自治机关的组成和自治权利等重要问题作出明确规定</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>军事科学院</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>习近平向中国人民解放军陆军、火箭军、战略支援部队授予军旗并致训词</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>农业银行</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>朱德致信中共中央，建议成立农业银行</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434744/index.html</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>农民协会</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>关于在不同地区实施土地法的策略问题，毛泽东致电刘少奇</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434791/index.html</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>农牧渔业部</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>中共中央、国务院转发农牧渔业部《关于开创社队企业新局面的报告》，同意将社队企业改称乡镇企业，提出发展乡镇企业的若干政策</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>包头钢铁公司</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>鞍山钢铁公司三大工程——大型轧钢厂、无缝钢管厂、七号炼铁炉举行开工生产典礼</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>北京军区</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>全军高级干部集训，重点研究战争初期方面军防御战役的组织与实施</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>为抗议驻华美军强暴北京大学先修班一女学生，北平学生举行示威游行</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>江泽民致信北京师范大学白寿彝教授，祝贺《中国通史》全部出版</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434751/index.html</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>十国集团</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>习近平出席在浙江杭州召开的二十国集团工商峰会开幕式并发表主旨演讲，提出建设创新、开放、联动、包容型世界经济，强调全球经济治理应该以平等为基础，更好反映世界经济格局新现实</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>华东野战军</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>刘伯承、邓小平率领晋冀鲁豫野战军主力强渡黄河，揭开战略进攻的序幕</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>华北军区</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-翌年1月31日　林彪、罗荣桓、聂荣臻等率东北野战军和华北军区第二、第三兵团以及华北、东北军区地方部队进行平津战役</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>南京政府</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>新华社发表毛泽东针对蒋介石的新年文告写的评论</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434821/index.html</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>南斯拉夫共产主义者联盟</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>邓小平会见南斯拉夫共产主义者联盟中央主席团主席马尔科维奇率领的南斯拉夫共产主义者联盟代表团时，谈到如何建设社会主义问题指出：关起门来无法搞社会主义</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434715/index.html</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>友好相处</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>胡锦涛在雅加达亚非峰会上提出，推动不同文明友好相处、平等对话、发展繁荣，共同构建一个和谐世界</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>反动集团</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>国务院发布《关于解散西藏地方政府的命令》，决定由西藏自治区筹备委员会行使西藏地方政府职权</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>台湾当局</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>中美公布关于建立外交关系的联合公报，宣布自1979年1月1日起互相承认并建立外交关系</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>合理布局</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>他强调，推进人的城镇化重要的环节在户籍制度，加快户籍制度改革，是涉及亿万农业转移人口的一项重大举措</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434671/index.html</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>和平共处</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>29日　周恩来在访问印度、缅甸期间，分别与印度总理尼赫鲁和缅甸总理吴努发表《联合声明》，共同倡导和平共处五项原则</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>国务院作出《关于金融体制改革的决定》</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>国务委员会</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>习近平对朝鲜民主主义人民共和国进行国事访问</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>国务院办公厅</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>国务院办公厅公布有关接待探亲台胞的办法</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>国家科学技术委员会</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>中共中央、国务院原则批准中央科学小组、国家科学技术委员会党组关于1963年-1972年科学技术发展规划的报告、科学技术发展规划纲要及科学技术事业规划</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>国家税务总局</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>经国务院批准，财政部、农业部、国家税务总局决定2004年降低农业税税率，并在部分粮食主产区进行免征农业税改革试点</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434732/index.html</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>国家统计局</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>国家统计局公布第七次全国人口普查主要数据，截至2020年11月1日零时，全国人口共141178万人</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>国家行政学院</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2019年春季学期中央党校(国家行政学院)中青年干部培训班开班</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434758/index.html</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>国家计划委员会</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>中共中央、国务院批准国家计划委员会《关于进口成套化纤、化肥技术设备的报告》</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434793/index.html</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>国民政府</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>中华民国国民政府在广州成立</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>国民政府军事委员会</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>国民党制造震惊中外的皖南事变</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434823/index.html</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>国民革命军</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>中华民国国民政府在广州成立</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>国防大学</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>习近平向中国人民解放军陆军、火箭军、战略支援部队授予军旗并致训词</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>国防委员会</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>一届全国人大一次会议举行</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>国防科技大学</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>由中国人民解放军国防科技大学研制成功的中国第一台亿次巨型计算机——“银河-Ⅰ”计算机在长沙通过国家鉴定，填补了国内巨型计算机研制的空白</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>国际关系学院</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>习近平对俄罗斯、坦桑尼亚、南非、刚果共和国进行国事访问，并出席在南非举行的金砖国家领导人第五次会晤</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>地方法院</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>中共中央办公厅、国务院办公厅印发《关于深化司法体制和社会体制改革的意见》</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>大兵团</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>根据国民党军调集五十万兵力采取“分进合击”的战略方针向中央革命根据地发起第四次“围剿”的情况，周恩来、朱德指挥红一方面军先后在黄陂、草台冈、东陂等地区重创国民党“围剿”军，取得了粉碎第四次“围剿”的重大胜利</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434815/index.html</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>小学教师</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>邓小平在同方毅、胡乔木等谈全国教育工作会议的报告时提出，学校要整顿，要多招一些学生，要开辟新的发展领域和行业</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434739/index.html</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>工农红军</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>毛泽东率部打破江西国民党军队对井冈山地区的进攻</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>工农联盟</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>中国共产党第四次全国代表大会在上海举行</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>巴黎公社</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>毛泽东在广州国民党政治讲习班纪念巴黎公社五十五周年集会上发表讲演，着重总结了巴黎公社失败的教训</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434775/index.html</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>延安大学</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>毛泽东在延安大学开学典礼上讲话</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434719/index.html</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>总体布局</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>《习近平关于实现中华民族伟大复兴的中国梦论述摘编》出版发行</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>总参谋部</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>新疆军区遵照军委总参谋部8月6日的批复公布成立新疆军区生产建设兵团</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>总司令部</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>中国工农红军总司令部成立，朱德任中国工农红军总司令，周恩来任总政治委员</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>总后勤部</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>解放军总参谋部、总政治部、总后勤部发出通知，规定预备役部队正式列入人民解放军建制序列</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>总工会</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>京汉铁路工人两万余人举行总罢工，全路一千二百公里顿时瘫痪</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>总指挥部</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>中共中央革命军事委员会发布命令，宣布红军改名为国民革命军第八路军(简称八路军)，下辖三个师，全军约4.6万人</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>总政治部</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>解放军总参谋部、总政治部、总后勤部发出通知，规定预备役部队正式列入人民解放军建制序列</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>我党我军</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>邓小平在北京病逝，享年93岁</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434807/index.html</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>战略部署</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>中共中央发出《关于加强农村思想政治工作的通知》</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434837/index.html</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>抗日军政大学</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>毛泽东为中国人民抗日军政大学第二期第二队学员题词：“要学习朱总司令：度量大如海，意志坚如钢</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434759/index.html</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>抗日红军大学</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>中国人民抗日军事政治大学(简称“抗大”)举行第二期开学典礼</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434838/index.html</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>政协全国委员会</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>政协全国委员会第49次常务委员会扩大会议在北京举行</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434470/434581/index.html</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>新疆军区</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>新疆军区遵照军委总参谋部8月6日的批复公布成立新疆军区生产建设兵团</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>新疆生产建设兵团</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>新疆军区遵照军委总参谋部8月6日的批复公布成立新疆军区生产建设兵团</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>日本公明党</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>邓小平会见日本公明党委员长竹入义胜率领的日本公明党第八次访华团时，就中国的民主与法制建设问题指出：民主和法制，这两个方面都应该加强</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434693/index.html</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>日本共产党</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>政党</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>毛泽东在会见日本共产党中央政治局委员听涛克己时，再次谈到两个中间地带问题</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434822/index.html</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>晋察冀军区</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>为适应解放战争胜利发展的形势，毛泽东、周恩来、任弼时率党中央领导机关自陕北米脂县杨家沟出发东渡黄河，与叶剑英、杨尚昆率领的中央后委会合</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434778/index.html</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>最高人民检察院</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>中央政治局常委会召开会议，专门听取全国人大常委会、国务院、全国政协、最高人民法院、最高人民检察院党组工作汇报</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>最高人民法院</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>中央政治局常委会召开会议，专门听取全国人大常委会、国务院、全国政协、最高人民法院、最高人民检察院党组工作汇报</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>有限公司</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>中国农业银行股份有限公司挂牌成立，至此，持续5年多的国有商业银行股份制改革基本完成</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>服务大局</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>习近平指出，过去的一年是党和国家历史上很不平凡的一年</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>朝鲜人民军</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>朝鲜人民军来到志愿军阵地上，互相祝贺、共同欢呼抗美斗争的伟大胜利</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434662/index.html</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>朝鲜劳动党</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>习近平对朝鲜民主主义人民共和国进行国事访问</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>武装集团</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>他强调，我军是执行党的政治任务的武装集团，军队党的建设必须高标准、严要求，努力走在全党前列</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434472/434483/index.html</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>海关总署</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>中央人民政府海关总署成立</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>海峡两岸关系协会</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>海峡两岸关系协会与台湾海峡交流基金会，就解决两岸事务性商谈中如何表述坚持一个中国原则的问题，达成“海峡两岸同属一个中国，共同努力谋求国家统一”的共识，后被称为“九二共识”</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>1991年4月22日 江泽民在四川考察工作时提出，要重视科学技术在现代战争中的作用</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434748/index.html</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>澳门特别行政区政府</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>本日，中华苏维埃中央政府及中共中央联名向南京、西安当局发出通电，重申和平解决西安事变的主张，并提出具体建议：双方军队暂以潼关为界，听候和平会议解决</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434473/434997/index.html</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>省军区</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>中共湘鄂川黔边临时省委、省军区在大庸(今张家界)成立(后迁至湖南永顺塔卧丁家院)，任弼时任省委书记兼省军区政治委员</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434472/434503/index.html</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>石油工业部</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>中共中央批转石油工业部党组《关于组织华北石油勘探会战的报告》</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434842/index.html</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>研究部署</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>中央政治局常委会会议专题听取有关国际金融危机情况和应采取应对措施的汇报</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>科学院</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>中国中医科学院研究员屠呦呦获得2015年诺贝尔生理学或医学奖</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>红三军团</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>毛泽东、朱德分析南昌的敌情和四面临水的地势，改变原来中央要求攻占南昌的计划，决定红一军团西渡赣江，乘虚向南昌对岸前进，避免了强攻中心城市可能遭受的损失，以实际行动抵制了中央攻打中心城市的军事冒险主义</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434658/index.html</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>红二军团</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>红六军团从湘赣革命根据地突围西征</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>红五军团</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>由红一军团和红五军团组成的东路军攻占漳州，俘敌一千六百余人，缴枪二千余支、飞机两架及其他大量军用物资，并筹得大批经费</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434746/index.html</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>红六军团</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>中旬　红军第六军团组建</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>红军前敌总指挥部</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>中共中央革命军事委员会发布命令，宣布红军改名为国民革命军第八路军(简称八路军)，下辖三个师，全军约4.6万人</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>红军大学</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>中共中央政治局召开常委会议，讨论建立红军大学问题</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434715/index.html</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>纽约联合国总部</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>习近平对美国进行国事访问并出席联合国成立70周年系列峰会</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>经济布局</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>国家批准实施《广西北部湾经济区发展规划》，这是党中央、国务院深入全面实施西部大开发战略、完善区域经济布局、促进全国区域协调发展和开放合作而作出的重大决策</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>统治集团</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>晋冀鲁豫军区集中主力3万余人，在山西长治地区(古称上党郡)实施的上党战役，一举歼灭入侵的阎锡山所部3万余人，击毙国民党军第七集团军副总司令彭毓斌，生俘第十九军军长史泽波，使阎锡山损失其总兵力的1/3</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434470/434583/index.html</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>美国众议院</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>邓小平在会见美国众议院银行、财政和城市事务委员会访华团时，就中美关系指出：我们欢迎美国政治家们，同时也欢迎包括不赞成中美建交在内的美国人士都来中国看看，以增进两国和两国人民之间的了解</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434819/index.html</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>美国国务院</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>毛泽东以中共中央主席名义发表《反对美国对蒋军事援助法案的声明》</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434687/index.html</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>美国政府</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>3月以来，针对美国政府单方面挑起的中美经贸摩擦，中国不得不采取中止关税减让义务、加征关税等反制措施，并在相互尊重、平等互利的原则基础上进行协商，坚决捍卫国家和人民利益</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>美国民主党</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>政党</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>邓小平会见以美国民主党众议员托马斯·路·阿什利为团长的美国众议院银行、财政和城市事务委员会访华团</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434819/index.html</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>联合政府</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>中共代表林伯渠在国民参政会上提出立即结束国民党一党统治、建立各抗日党派民主联合政府的主张</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>苏区中央局</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>中共中央成立南方局，重新成立北方局</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>苏维埃政府</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>中共广东省委书记张太雷和叶挺、叶剑英等领导发动广州起义，成立广州苏维埃政府</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>苏联政府</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>苏联政府决定同新中国建立外交关系</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>苏联红军</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>毛泽东就庆祝苏联红军成立二十五周年与红军反攻的伟大胜利，致电斯大林、联共中央和红军将士们</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434809/index.html</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>葡萄牙共和国政府</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>中葡两国政府在北京正式签署《中华人民共和国政府和葡萄牙共和国政府关于澳门问题的联合声明》，确认中国政府于1999年12月20日对澳门恢复行使主权</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>财政经济委员会</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>中央人民政府海关总署成立</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>财经委员会</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>习近平在中央财经委员会第七次会议上讲话提出，要构建以国内大循环为主体、国内国际双循环相互促进的新发展格局</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>钢铁公司</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>鞍山钢铁公司三大工程——大型轧钢厂、无缝钢管厂、七号炼铁炉举行开工生产典礼</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>陆海空军</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>军队</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>为显示中国人民完全有决心、有办法、有能力维护祖国统一，震慑“台独”势力，人民解放军向东海、南海进行发射导弹训练，并在东海、南海进行海空实弹演习和在台湾海峡进行陆海空军联合演习</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>青年团</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>广东海丰县农会成立</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434818/index.html</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>香港特别行政区基本法起草委员会</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>香港特别行政区基本法起草委员会第九次会议在北京举行</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434801/index.html</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/excel/organization.xlsx
+++ b/data/excel/organization.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1420,17 +1420,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>中国工农红军第二十五军</t>
+          <t>八路军第一二〇师</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>红二十五军</t>
+          <t>一二〇师</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1931年10月</t>
+          <t>1937年8月</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>鄂豫皖苏区组建的红军部队，长征中最先到达陕北。</t>
+          <t>八路军主力师之一，由红二方面军等部改编，贺龙任师长，开创晋西北抗日根据地。</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1455,17 +1455,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>中国人民解放军第四野战军</t>
+          <t>八路军第一二九师</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>四野</t>
+          <t>一二九师</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1949年3月</t>
+          <t>1937年8月</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>解放战争时期人民解放军五大野战军之一，参与辽沈、平津战役。</t>
+          <t>八路军主力师之一，由红四方面军等部改编，刘伯承任师长、邓小平任政治委员。</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1490,27 +1490,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>中国人民解放军第三野战军</t>
+          <t>中国社会主义青年团</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>三野</t>
+          <t>社会主义青年团</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1949年2月</t>
+          <t>1922年5月</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>解放战争时期人民解放军五大野战军之一，参与淮海、渡江战役。</t>
+          <t>中国共产党领导的青年组织，1925 年改名为中国共产主义青年团。</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>中国人民解放军第二野战军</t>
+          <t>中国工农红军第二十五军</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>二野</t>
+          <t>红二十五军</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1949年2月</t>
+          <t>1931年10月</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>解放战争时期人民解放军五大野战军之一，由晋冀鲁豫野战军发展而来。</t>
+          <t>鄂豫皖苏区组建的红军部队，长征中最先到达陕北。</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1560,17 +1560,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>中国人民解放军第一野战军</t>
+          <t>中国人民解放军第四野战军</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>一野</t>
+          <t>四野</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1949年2月</t>
+          <t>1949年3月</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>解放战争时期人民解放军五大野战军之一，由西北野战军发展而来。</t>
+          <t>解放战争时期人民解放军五大野战军之一，参与辽沈、平津战役。</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1595,27 +1595,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>中华全国妇女联合会</t>
+          <t>中国人民解放军第三野战军</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>全国妇联</t>
+          <t>三野</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1949年3月</t>
+          <t>1949年2月</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>中国共产党领导的全国各族各界妇女的群众组织。</t>
+          <t>解放战争时期人民解放军五大野战军之一，参与淮海、渡江战役。</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1630,27 +1630,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>中华全国青年联合会</t>
+          <t>中国人民解放军第二野战军</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>全国青联</t>
+          <t>二野</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1949年5月</t>
+          <t>1949年2月</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>中国共产党领导的全国各族各界青年的群众组织。</t>
+          <t>解放战争时期人民解放军五大野战军之一，由晋冀鲁豫野战军发展而来。</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1665,27 +1665,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>中国少年先锋队</t>
+          <t>中国人民解放军第一野战军</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>少先队</t>
+          <t>一野</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1949年10月13日</t>
+          <t>1949年2月</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>中国共产党委托中国共产主义青年团领导的中国少年儿童的群众组织。</t>
+          <t>解放战争时期人民解放军五大野战军之一，由西北野战军发展而来。</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1700,27 +1700,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>共产国际</t>
+          <t>中华全国妇女联合会</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>第三国际</t>
+          <t>全国妇联</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1919年3月</t>
+          <t>1949年3月</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1919 年成立的国际共产主义组织，曾对中国共产党的创建与早期活动给予帮助。</t>
+          <t>中国共产党领导的全国各族各界妇女的群众组织。</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1735,27 +1735,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>中国国民党</t>
+          <t>中华全国青年联合会</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>国民党</t>
+          <t>全国青联</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1919年10月</t>
+          <t>1949年5月</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>政党</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>由孙中山改组成立的政党，曾两度与中国共产党合作。</t>
+          <t>中国共产党领导的全国各族各界青年的群众组织。</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1770,27 +1770,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>中国民主同盟</t>
+          <t>中国少年先锋队</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>民盟</t>
+          <t>少先队</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1941年3月</t>
+          <t>1949年10月13日</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>政党</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>中国的民主党派之一，由文教界知识分子为主组成。</t>
+          <t>中国共产党委托中国共产主义青年团领导的中国少年儿童的群众组织。</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1805,27 +1805,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>中国国民党革命委员会</t>
+          <t>共产国际</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>民革</t>
+          <t>第三国际</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1948年1月</t>
+          <t>1919年3月</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>政党</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>中国的民主党派之一，由原中国国民党民主派人士组成。</t>
+          <t>1919 年成立的国际共产主义组织，曾对中国共产党的创建与早期活动给予帮助。</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1840,105 +1840,129 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>三五九旅</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+          <t>中国国民党</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>国民党</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1919年10月</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>政党</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>为克服经济上的严重困难，中共中央在延安召开生产动员大会，毛泽东发出“自己动手”的号召</t>
+          <t>由孙中山改组成立的政党，曾两度与中国共产党合作。</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>上海市人民政府</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+          <t>中国民主同盟</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>民盟</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1941年3月</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>政党</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>国务院批转上海市人民政府、国务院改造振兴上海调研组《关于上海经济发展战略的汇报提纲》，并发出通知指出，改造、振兴上海是关系我国四化建设的大事</t>
+          <t>中国的民主党派之一，由文教界知识分子为主组成。</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434796/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>世界银行</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+          <t>中国国民党革命委员会</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>民革</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1948年1月</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>政党</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>中国恢复在世界银行的代表权</t>
+          <t>中国的民主党派之一，由原中国国民党民主派人士组成。</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>中共中央党校</t>
+          <t>三五九旅</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>毛泽东在中共中央党校作题为《反对投降主义》的讲话</t>
+          <t>为克服经济上的严重困难，中共中央在延安召开生产动员大会，毛泽东发出“自己动手”的号召</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434793/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1948,7 +1972,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>中共中央北方局</t>
+          <t>上海市人民政府</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1960,12 +1984,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>中共中央北方局在太原组建新的领导机关</t>
+          <t>国务院批转上海市人民政府、国务院改造振兴上海调研组《关于上海经济发展战略的汇报提纲》，并发出通知指出，改造、振兴上海是关系我国四化建设的大事</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434796/index.html</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -1975,7 +1999,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>中共中央政治局常委会</t>
+          <t>世界银行</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1987,12 +2011,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>中共中央政治局常委会召开会议，专门听取全国人大常委会、国务院、全国政协、最高人民法院、最高人民检察院党组工作汇报</t>
+          <t>中国恢复在世界银行的代表权</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2002,7 +2026,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>中共中央统战部</t>
+          <t>中共中央党校</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2014,12 +2038,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>陈云在中共中央统战部讨论工商联工作会议上作总结讲话</t>
+          <t>毛泽东在中共中央党校作题为《反对投降主义》的讲话</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434654/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434793/index.html</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2029,7 +2053,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>中华人民共和国中央人民政府</t>
+          <t>中共中央北方局</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2041,7 +2065,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议第一届全体会议在北平举行</t>
+          <t>中共中央北方局在太原组建新的领导机关</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2056,7 +2080,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>中华人民共和国中央军事委员会</t>
+          <t>中共中央政治局常委会</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2068,12 +2092,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>国务院、中央军委发布公告：中国人民解放军驻香港特别行政区部队组建完成</t>
+          <t>中共中央政治局常委会召开会议，专门听取全国人大常委会、国务院、全国政协、最高人民法院、最高人民检察院党组工作汇报</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434845/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2083,7 +2107,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>中华人民共和国全国人民代表大会</t>
+          <t>中共中央统战部</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2095,12 +2119,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>《中华人民共和国全国人民代表大会及地方各级人民代表大会选举法》公布施行</t>
+          <t>陈云在中共中央统战部讨论工商联工作会议上作总结讲话</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434654/index.html</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2110,7 +2134,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>中华人民共和国政府</t>
+          <t>中华人民共和国中央人民政府</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2122,7 +2146,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>中缅两国签订《中华人民共和国政府和缅甸联邦政府关于两国边界问题的协定》、《中华人民共和国和缅甸联邦之间的友好和互不侵犯条约》</t>
+          <t>中国人民政治协商会议第一届全体会议在北平举行</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2137,7 +2161,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>中华全国供销合作总社</t>
+          <t>中华人民共和国中央军事委员会</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2149,12 +2173,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>中华全国合作社第一次代表大会在北京举行</t>
+          <t>国务院、中央军委发布公告：中国人民解放军驻香港特别行政区部队组建完成</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434654/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434845/index.html</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2164,24 +2188,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>中华全国学生联合会</t>
+          <t>中华人民共和国全国人民代表大会</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>中华全国学生联合会在北平宣布成立</t>
+          <t>《中华人民共和国全国人民代表大会及地方各级人民代表大会选举法》公布施行</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434758/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2191,24 +2215,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>中华全国工商业联合会</t>
+          <t>中华人民共和国政府</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>第一届中华全国工商业联合会会员代表大会开幕</t>
+          <t>中缅两国签订《中华人民共和国政府和缅甸联邦政府关于两国边界问题的协定》、《中华人民共和国和缅甸联邦之间的友好和互不侵犯条约》</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434565/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2218,24 +2242,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>中原军区</t>
+          <t>中华全国供销合作总社</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>毛泽东、朱德发布《向全国进军的命令》</t>
+          <t>中华全国合作社第一次代表大会在北京举行</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434654/index.html</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2245,24 +2269,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>中国人民大学</t>
+          <t>中华全国学生联合会</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>刘少奇签发中共中央关于成立中国人民大学的决定</t>
+          <t>中华全国学生联合会在北平宣布成立</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434840/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434758/index.html</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2272,24 +2296,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>中国人民解放军总部</t>
+          <t>中华全国工商业联合会</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>中国人民解放军总部发表宣言，提出“打倒蒋介石，解放全中国”的口号</t>
+          <t>第一届中华全国工商业联合会会员代表大会开幕</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434565/index.html</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2299,7 +2323,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>中国人民解放军海军</t>
+          <t>中原军区</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2311,7 +2335,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>根据联合国安理会有关决议，中国人民解放军海军首批舰艇编队赴亚丁湾、索马里海域执行护航任务</t>
+          <t>毛泽东、朱德发布《向全国进军的命令》</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2326,24 +2350,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>中国人民解放军空军</t>
+          <t>中国人民大学</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>中国人民解放军空军领导机构成立</t>
+          <t>刘少奇签发中共中央关于成立中国人民大学的决定</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434840/index.html</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2353,7 +2377,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>中国人民银行</t>
+          <t>中国人民解放军总部</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2365,7 +2389,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>中国人民银行成立并发行人民币</t>
+          <t>中国人民解放军总部发表宣言，提出“打倒蒋介石，解放全中国”的口号</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2380,19 +2404,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>中国共产党中央委员会</t>
+          <t>中国人民解放军海军</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>中央政治局扩大会议召开</t>
+          <t>根据联合国安理会有关决议，中国人民解放军海军首批舰艇编队赴亚丁湾、索马里海域执行护航任务</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2407,24 +2431,24 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>中国工会</t>
+          <t>中国人民解放军空军</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>中国工会第七次全国代表大会在北京举行</t>
+          <t>中国人民解放军空军领导机构成立</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434697/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -2434,7 +2458,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>中国工程院</t>
+          <t>中国人民银行</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2446,7 +2470,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>习近平在中国科学院第二十次院士大会、中国工程院第十五次院士大会、中国科协第十次全国代表大会上讲话指出，要加快建设科技强国，实现高水平科技自立自强</t>
+          <t>中国人民银行成立并发行人民币</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2461,24 +2485,24 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>中国新民主主义青年团</t>
+          <t>中国共产党中央委员会</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>中国新民主主义青年团第一次全国代表大会在北平召开</t>
+          <t>中央政治局扩大会议召开</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434737/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -2488,7 +2512,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>中国社会主义青年团</t>
+          <t>中国工会</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2500,12 +2524,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>中国社会主义青年团第一次全国代表大会在广州召开，中国社会主义青年团成立</t>
+          <t>中国工会第七次全国代表大会在北京举行</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434697/index.html</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -2515,24 +2539,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>中国科学技术协会</t>
+          <t>中国工程院</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>中国科学技术协会第四次全国代表大会在北京举行</t>
+          <t>习近平在中国科学院第二十次院士大会、中国工程院第十五次院士大会、中国科协第十次全国代表大会上讲话指出，要加快建设科技强国，实现高水平科技自立自强</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434718/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -2542,24 +2566,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>中国科学院</t>
+          <t>中国新民主主义青年团</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>中共中央发出《关于召开全国科学大会的通知》，要求抓紧落实党的知识分子政策，迅速恢复被撤掉的科研机构，恢复科研人员的技术职称，建立考核制度，实行技术岗位责任制</t>
+          <t>中国新民主主义青年团第一次全国代表大会在北平召开</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434737/index.html</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -2569,24 +2593,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>中国空军</t>
+          <t>中国科学技术协会</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>中国政府宣布划设东海防空识别区，并发布航空器识别规则公告和识别区示意图</t>
+          <t>中国科学技术协会第四次全国代表大会在北京举行</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434718/index.html</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -2596,7 +2620,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>中央人民政府</t>
+          <t>中国科学院</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2608,7 +2632,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议第一届全体会议在北平举行</t>
+          <t>中共中央发出《关于召开全国科学大会的通知》，要求抓紧落实党的知识分子政策，迅速恢复被撤掉的科研机构，恢复科研人员的技术职称，建立考核制度，实行技术岗位责任制</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2623,19 +2647,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>中央人民政府政务院</t>
+          <t>中国空军</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>中华人民共和国中央人民政府成立</t>
+          <t>中国政府宣布划设东海防空识别区，并发布航空器识别规则公告和识别区示意图</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2650,7 +2674,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>中央人民政府</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2662,7 +2686,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>中央党校内部刊物《理论动态》刊登《实践是检验真理的唯一标准》一文</t>
+          <t>中国人民政治协商会议第一届全体会议在北平举行</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2677,7 +2701,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>中央军事委员会</t>
+          <t>中央人民政府政务院</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2689,7 +2713,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>中共七届一中全会选举毛泽东、朱德、刘少奇、周恩来、任弼时为中央书记处书记，毛泽东为中央委员会主席、中央政治局主席、中央书记处主席</t>
+          <t>中华人民共和国中央人民政府成立</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2704,7 +2728,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>中央宣传部</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2716,7 +2740,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>中央政治局召开会议</t>
+          <t>中央党校内部刊物《理论动态》刊登《实践是检验真理的唯一标准》一文</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2731,7 +2755,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>中央政治局常委会</t>
+          <t>中央军事委员会</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2743,7 +2767,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>中央政治局常委会会议专题研究新疆稳定工作</t>
+          <t>中共七届一中全会选举毛泽东、朱德、刘少奇、周恩来、任弼时为中央书记处书记，毛泽东为中央委员会主席、中央政治局主席、中央书记处主席</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2758,7 +2782,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>中央政法委员会</t>
+          <t>中央宣传部</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2770,12 +2794,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>中共中央发出《关于成立中央政法委员会的通知》</t>
+          <t>中央政治局召开会议</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434841/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -2785,7 +2809,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>中央民族学院</t>
+          <t>中央政治局常委会</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2797,7 +2821,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>政务院第六十次政务会议批准《培养少数民族干部试行方案》和《筹办中央民族学院试行方案》</t>
+          <t>中央政治局常委会会议专题研究新疆稳定工作</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2812,7 +2836,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>中央纪律检查委员会</t>
+          <t>中央政法委员会</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2824,12 +2848,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>中共中央决定成立中央及各级党的纪律检查委员会，朱德兼任中央纪律检查委员会书记</t>
+          <t>中共中央发出《关于成立中央政法委员会的通知》</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434841/index.html</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -2839,7 +2863,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>中央组织部</t>
+          <t>中央民族学院</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2851,7 +2875,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>中共中央办公厅转发中央组织部、中央宣传部《关于在党的基层组织和党员中深入开展创先争优活动的意见》，对开展创先争优活动作出部署</t>
+          <t>政务院第六十次政务会议批准《培养少数民族干部试行方案》和《筹办中央民族学院试行方案》</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2866,7 +2890,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>中央美术学院</t>
+          <t>中央纪律检查委员会</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2878,12 +2902,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>习近平主持召开中央全面深化改革领导小组第二十七次会议强调，当前和今后一个时期，是全面深化改革的施工高峰期，是落实改革任务的攻坚期，抓谋划、抓统筹、抓落实的任务依然艰巨繁重</t>
+          <t>中共中央决定成立中央及各级党的纪律检查委员会，朱德兼任中央纪律检查委员会书记</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434469/434633/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -2893,7 +2917,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>中央银行</t>
+          <t>中央组织部</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2905,7 +2929,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>国务院作出《关于金融体制改革的决定》</t>
+          <t>中共中央办公厅转发中央组织部、中央宣传部《关于在党的基层组织和党员中深入开展创先争优活动的意见》，对开展创先争优活动作出部署</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2920,7 +2944,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>中央革命军事委员会</t>
+          <t>中央美术学院</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -2932,12 +2956,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>在以周恩来为书记的中共中央前敌委员会领导下，贺龙、叶挺、朱德、刘伯承等率领党所掌握和影响的军队两万余人，在江西南昌打响武装反抗国民党反动派的第一枪</t>
+          <t>习近平主持召开中央全面深化改革领导小组第二十七次会议强调，当前和今后一个时期，是全面深化改革的施工高峰期，是落实改革任务的攻坚期，抓谋划、抓统筹、抓落实的任务依然艰巨繁重</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434469/434633/index.html</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -2947,7 +2971,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>中央顾问委员会</t>
+          <t>中央银行</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2959,7 +2983,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>中国共产党第十二次全国代表大会举行</t>
+          <t>国务院作出《关于金融体制改革的决定》</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2974,7 +2998,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>中开新局</t>
+          <t>中央革命军事委员会</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2986,12 +3010,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>习近平在中央党校(国家行政学院)中青年干部培训班开班式上发表讲话强调，历史总是在不断解决问题中前进的</t>
+          <t>在以周恩来为书记的中共中央前敌委员会领导下，贺龙、叶挺、朱德、刘伯承等率领党所掌握和影响的军队两万余人，在江西南昌打响武装反抗国民党反动派的第一枪</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434552/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -3001,7 +3025,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>九届全国人大</t>
+          <t>中央顾问委员会</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3013,7 +3037,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>九届全国人大一次会议举行</t>
+          <t>中国共产党第十二次全国代表大会举行</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3028,7 +3052,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>九届全国人大常委会</t>
+          <t>中开新局</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3040,12 +3064,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>六届全国人大二次会议通过《中华人民共和国民族区域自治法》</t>
+          <t>习近平在中央党校(国家行政学院)中青年干部培训班开班式上发表讲话强调，历史总是在不断解决问题中前进的</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434471/434552/index.html</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -3055,7 +3079,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>人民公社</t>
+          <t>九届全国人大</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3067,7 +3091,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>中共中央发出《关于农村人民公社当前政策问题的紧急指示信》，要求坚决纠正农村人民公社的“共产风”</t>
+          <t>九届全国人大一次会议举行</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3082,7 +3106,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>人民日报社</t>
+          <t>九届全国人大常委会</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3094,12 +3118,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>由《晋察冀日报》和晋冀鲁豫《人民日报》合并而成的中共华北局机关报《人民日报》在河北省平山县里庄创刊，毛泽东为《人民日报》题写报头</t>
+          <t>六届全国人大二次会议通过《中华人民共和国民族区域自治法》</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434680/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -3109,7 +3133,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>人民法院</t>
+          <t>人民公社</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3121,12 +3145,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>中共中央发出通知，根据五届人大一次会议通过的宪法，重新设置人民检察院，与公安机关、人民法院互相配合，又相互制约，同各种违法乱纪行为作斗争</t>
+          <t>中共中央发出《关于农村人民公社当前政策问题的紧急指示信》，要求坚决纠正农村人民公社的“共产风”</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434719/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -3136,24 +3160,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>人民解放军</t>
+          <t>人民日报社</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>中华人民共和国中央人民政府成立</t>
+          <t>由《晋察冀日报》和晋冀鲁豫《人民日报》合并而成的中共华北局机关报《人民日报》在河北省平山县里庄创刊，毛泽东为《人民日报》题写报头</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434680/index.html</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -3163,7 +3187,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>人民解放军总部</t>
+          <t>人民法院</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3175,12 +3199,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>中央政治局会议在陕北清涧枣林沟召开，讨论中央机关行动问题</t>
+          <t>中共中央发出通知，根据五届人大一次会议通过的宪法，重新设置人民检察院，与公安机关、人民法院互相配合，又相互制约，同各种违法乱纪行为作斗争</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434719/index.html</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -3190,7 +3214,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>侵华日军</t>
+          <t>人民解放军</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3202,7 +3226,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>日本代表在投降书上签字</t>
+          <t>中华人民共和国中央人民政府成立</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3217,7 +3241,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>党和政府</t>
+          <t>人民解放军总部</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3229,7 +3253,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>上旬　应朝鲜党和政府的请求，中共中央作出抗美援朝、保家卫国的战略决策</t>
+          <t>中央政治局会议在陕北清涧枣林沟召开，讨论中央机关行动问题</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3244,19 +3268,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>全国人大常委会</t>
+          <t>侵华日军</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>一届全国人大一次会议举行</t>
+          <t>日本代表在投降书上签字</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3271,7 +3295,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>全国人民代表大会常务委员会</t>
+          <t>党和政府</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3283,12 +3307,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>邓小平在全国政协讨论五届全国人大常委会五次会议通过的《全国人民代表大会常务委员会告台湾同胞书》的座谈会上讲话，提出把解决台湾问题、完成祖国统一大业提上具体日程</t>
+          <t>上旬　应朝鲜党和政府的请求，中共中央作出抗美援朝、保家卫国的战略决策</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434818/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -3298,24 +3322,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>全国工会</t>
+          <t>全国人大常委会</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>朱德在全国工会工作会议开幕式上讲话</t>
+          <t>一届全国人大一次会议举行</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434657/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -3325,24 +3349,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>全国总工会</t>
+          <t>全国人民代表大会常务委员会</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>全国总工会、共青团中央等九单位联合向全国人民特别是青少年发出倡议，开展以讲文明、讲礼貌、讲卫生、讲秩序、讲道德和心灵美、语言美、行为美、环境美为主要内容的“五讲四美”文明礼貌活动</t>
+          <t>邓小平在全国政协讨论五届全国人大常委会五次会议通过的《全国人民代表大会常务委员会告台湾同胞书》的座谈会上讲话，提出把解决台湾问题、完成祖国统一大业提上具体日程</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434818/index.html</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -3352,24 +3376,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>八国集团</t>
+          <t>全国工会</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2007年6月8日 胡锦涛在八国集团同发展中国家领导人对话会议上讲话，提出中国对气候变化问题的原则立场</t>
+          <t>朱德在全国工会工作会议开幕式上讲话</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434673/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434657/index.html</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -3379,19 +3403,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>八届全国人大</t>
+          <t>全国总工会</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>八届全国人大一次会议举行</t>
+          <t>全国总工会、共青团中央等九单位联合向全国人民特别是青少年发出倡议，开展以讲文明、讲礼貌、讲卫生、讲秩序、讲道德和心灵美、语言美、行为美、环境美为主要内容的“五讲四美”文明礼貌活动</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3406,7 +3430,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>八届全国人大常委会</t>
+          <t>八国集团</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3418,12 +3442,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>八届全国人大常委会第八次会议通过《中华人民共和国劳动法》</t>
+          <t>2007年6月8日 胡锦涛在八国集团同发展中国家领导人对话会议上讲话，提出中国对气候变化问题的原则立场</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434673/index.html</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -3433,7 +3457,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>八路军总部</t>
+          <t>八届全国人大</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3445,7 +3469,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>八路军第一二九师主力同冀南军区部队一起进行反“扫荡”作战，巩固了冀南抗日根据地</t>
+          <t>八届全国人大一次会议举行</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3460,7 +3484,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>内蒙古自治区人民政府</t>
+          <t>八届全国人大常委会</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -3472,7 +3496,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>《中华人民共和国民族区域自治实施纲要》公布施行，对民族自治地方的建立、自治机关的组成和自治权利等重要问题作出明确规定</t>
+          <t>八届全国人大常委会第八次会议通过《中华人民共和国劳动法》</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3487,7 +3511,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>军事科学院</t>
+          <t>八路军总部</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -3499,7 +3523,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>习近平向中国人民解放军陆军、火箭军、战略支援部队授予军旗并致训词</t>
+          <t>八路军第一二九师主力同冀南军区部队一起进行反“扫荡”作战，巩固了冀南抗日根据地</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3514,7 +3538,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>农业银行</t>
+          <t>内蒙古自治区人民政府</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -3526,12 +3550,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>朱德致信中共中央，建议成立农业银行</t>
+          <t>《中华人民共和国民族区域自治实施纲要》公布施行，对民族自治地方的建立、自治机关的组成和自治权利等重要问题作出明确规定</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434744/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -3541,24 +3565,24 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>农民协会</t>
+          <t>军事科学院</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>关于在不同地区实施土地法的策略问题，毛泽东致电刘少奇</t>
+          <t>习近平向中国人民解放军陆军、火箭军、战略支援部队授予军旗并致训词</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434791/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -3568,7 +3592,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>农牧渔业部</t>
+          <t>农业银行</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -3580,12 +3604,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>中共中央、国务院转发农牧渔业部《关于开创社队企业新局面的报告》，同意将社队企业改称乡镇企业，提出发展乡镇企业的若干政策</t>
+          <t>朱德致信中共中央，建议成立农业银行</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434744/index.html</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -3595,24 +3619,24 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>包头钢铁公司</t>
+          <t>农民协会</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>鞍山钢铁公司三大工程——大型轧钢厂、无缝钢管厂、七号炼铁炉举行开工生产典礼</t>
+          <t>关于在不同地区实施土地法的策略问题，毛泽东致电刘少奇</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434791/index.html</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -3622,19 +3646,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>北京军区</t>
+          <t>农牧渔业部</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>全军高级干部集训，重点研究战争初期方面军防御战役的组织与实施</t>
+          <t>中共中央、国务院转发农牧渔业部《关于开创社队企业新局面的报告》，同意将社队企业改称乡镇企业，提出发展乡镇企业的若干政策</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3649,7 +3673,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>包头钢铁公司</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -3661,7 +3685,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>为抗议驻华美军强暴北京大学先修班一女学生，北平学生举行示威游行</t>
+          <t>鞍山钢铁公司三大工程——大型轧钢厂、无缝钢管厂、七号炼铁炉举行开工生产典礼</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3676,24 +3700,24 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>北京师范大学</t>
+          <t>北京军区</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>江泽民致信北京师范大学白寿彝教授，祝贺《中国通史》全部出版</t>
+          <t>全军高级干部集训，重点研究战争初期方面军防御战役的组织与实施</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434751/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -3703,7 +3727,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>十国集团</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -3715,7 +3739,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>习近平出席在浙江杭州召开的二十国集团工商峰会开幕式并发表主旨演讲，提出建设创新、开放、联动、包容型世界经济，强调全球经济治理应该以平等为基础，更好反映世界经济格局新现实</t>
+          <t>为抗议驻华美军强暴北京大学先修班一女学生，北平学生举行示威游行</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3730,24 +3754,24 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>华东野战军</t>
+          <t>北京师范大学</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>刘伯承、邓小平率领晋冀鲁豫野战军主力强渡黄河，揭开战略进攻的序幕</t>
+          <t>江泽民致信北京师范大学白寿彝教授，祝贺《中国通史》全部出版</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434751/index.html</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -3757,19 +3781,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>华北军区</t>
+          <t>十国集团</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>-翌年1月31日　林彪、罗荣桓、聂荣臻等率东北野战军和华北军区第二、第三兵团以及华北、东北军区地方部队进行平津战役</t>
+          <t>习近平出席在浙江杭州召开的二十国集团工商峰会开幕式并发表主旨演讲，提出建设创新、开放、联动、包容型世界经济，强调全球经济治理应该以平等为基础，更好反映世界经济格局新现实</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3784,24 +3808,24 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>南京政府</t>
+          <t>华东野战军</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>新华社发表毛泽东针对蒋介石的新年文告写的评论</t>
+          <t>刘伯承、邓小平率领晋冀鲁豫野战军主力强渡黄河，揭开战略进攻的序幕</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434821/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -3811,24 +3835,24 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>南斯拉夫共产主义者联盟</t>
+          <t>华北军区</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>邓小平会见南斯拉夫共产主义者联盟中央主席团主席马尔科维奇率领的南斯拉夫共产主义者联盟代表团时，谈到如何建设社会主义问题指出：关起门来无法搞社会主义</t>
+          <t>-翌年1月31日　林彪、罗荣桓、聂荣臻等率东北野战军和华北军区第二、第三兵团以及华北、东北军区地方部队进行平津战役</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434715/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -3838,7 +3862,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>友好相处</t>
+          <t>南京政府</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -3850,12 +3874,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>胡锦涛在雅加达亚非峰会上提出，推动不同文明友好相处、平等对话、发展繁荣，共同构建一个和谐世界</t>
+          <t>新华社发表毛泽东针对蒋介石的新年文告写的评论</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434821/index.html</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -3865,24 +3889,24 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>反动集团</t>
+          <t>南斯拉夫共产主义者联盟</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>国务院发布《关于解散西藏地方政府的命令》，决定由西藏自治区筹备委员会行使西藏地方政府职权</t>
+          <t>邓小平会见南斯拉夫共产主义者联盟中央主席团主席马尔科维奇率领的南斯拉夫共产主义者联盟代表团时，谈到如何建设社会主义问题指出：关起门来无法搞社会主义</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434715/index.html</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -3892,7 +3916,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>台湾当局</t>
+          <t>友好相处</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -3904,7 +3928,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>中美公布关于建立外交关系的联合公报，宣布自1979年1月1日起互相承认并建立外交关系</t>
+          <t>胡锦涛在雅加达亚非峰会上提出，推动不同文明友好相处、平等对话、发展繁荣，共同构建一个和谐世界</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -3919,7 +3943,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>合理布局</t>
+          <t>反动集团</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -3931,12 +3955,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>他强调，推进人的城镇化重要的环节在户籍制度，加快户籍制度改革，是涉及亿万农业转移人口的一项重大举措</t>
+          <t>国务院发布《关于解散西藏地方政府的命令》，决定由西藏自治区筹备委员会行使西藏地方政府职权</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434671/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -3946,7 +3970,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>和平共处</t>
+          <t>台湾当局</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -3958,7 +3982,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>29日　周恩来在访问印度、缅甸期间，分别与印度总理尼赫鲁和缅甸总理吴努发表《联合声明》，共同倡导和平共处五项原则</t>
+          <t>中美公布关于建立外交关系的联合公报，宣布自1979年1月1日起互相承认并建立外交关系</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -3973,7 +3997,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>合理布局</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -3985,12 +4009,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>国务院作出《关于金融体制改革的决定》</t>
+          <t>他强调，推进人的城镇化重要的环节在户籍制度，加快户籍制度改革，是涉及亿万农业转移人口的一项重大举措</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434671/index.html</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -4000,7 +4024,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>国务委员会</t>
+          <t>和平共处</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4012,7 +4036,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>习近平对朝鲜民主主义人民共和国进行国事访问</t>
+          <t>29日　周恩来在访问印度、缅甸期间，分别与印度总理尼赫鲁和缅甸总理吴努发表《联合声明》，共同倡导和平共处五项原则</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4027,7 +4051,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>国务院办公厅</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4039,7 +4063,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>国务院办公厅公布有关接待探亲台胞的办法</t>
+          <t>国务院作出《关于金融体制改革的决定》</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4054,7 +4078,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>国家科学技术委员会</t>
+          <t>国务委员会</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4066,7 +4090,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>中共中央、国务院原则批准中央科学小组、国家科学技术委员会党组关于1963年-1972年科学技术发展规划的报告、科学技术发展规划纲要及科学技术事业规划</t>
+          <t>习近平对朝鲜民主主义人民共和国进行国事访问</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4081,7 +4105,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>国家税务总局</t>
+          <t>国务院办公厅</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4093,12 +4117,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>经国务院批准，财政部、农业部、国家税务总局决定2004年降低农业税税率，并在部分粮食主产区进行免征农业税改革试点</t>
+          <t>国务院办公厅公布有关接待探亲台胞的办法</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434732/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -4108,7 +4132,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>国家统计局</t>
+          <t>国家科学技术委员会</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4120,7 +4144,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>国家统计局公布第七次全国人口普查主要数据，截至2020年11月1日零时，全国人口共141178万人</t>
+          <t>中共中央、国务院原则批准中央科学小组、国家科学技术委员会党组关于1963年-1972年科学技术发展规划的报告、科学技术发展规划纲要及科学技术事业规划</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4135,7 +4159,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>国家行政学院</t>
+          <t>国家税务总局</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4147,12 +4171,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2019年春季学期中央党校(国家行政学院)中青年干部培训班开班</t>
+          <t>经国务院批准，财政部、农业部、国家税务总局决定2004年降低农业税税率，并在部分粮食主产区进行免征农业税改革试点</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434758/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434732/index.html</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -4162,7 +4186,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>国家计划委员会</t>
+          <t>国家统计局</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4174,12 +4198,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>中共中央、国务院批准国家计划委员会《关于进口成套化纤、化肥技术设备的报告》</t>
+          <t>国家统计局公布第七次全国人口普查主要数据，截至2020年11月1日零时，全国人口共141178万人</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434793/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -4189,7 +4213,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>国民政府</t>
+          <t>国家行政学院</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -4201,12 +4225,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>中华民国国民政府在广州成立</t>
+          <t>2019年春季学期中央党校(国家行政学院)中青年干部培训班开班</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434758/index.html</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4216,7 +4240,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>国民政府军事委员会</t>
+          <t>国家计划委员会</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -4228,12 +4252,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>国民党制造震惊中外的皖南事变</t>
+          <t>中共中央、国务院批准国家计划委员会《关于进口成套化纤、化肥技术设备的报告》</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434823/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434793/index.html</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4243,14 +4267,14 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>国民革命军</t>
+          <t>国民政府</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4270,7 +4294,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>国防大学</t>
+          <t>国民政府军事委员会</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -4282,12 +4306,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>习近平向中国人民解放军陆军、火箭军、战略支援部队授予军旗并致训词</t>
+          <t>国民党制造震惊中外的皖南事变</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434823/index.html</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4297,19 +4321,19 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>国防委员会</t>
+          <t>国民革命军</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>一届全国人大一次会议举行</t>
+          <t>中华民国国民政府在广州成立</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4324,7 +4348,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>国防科技大学</t>
+          <t>国防大学</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -4336,7 +4360,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>由中国人民解放军国防科技大学研制成功的中国第一台亿次巨型计算机——“银河-Ⅰ”计算机在长沙通过国家鉴定，填补了国内巨型计算机研制的空白</t>
+          <t>习近平向中国人民解放军陆军、火箭军、战略支援部队授予军旗并致训词</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4351,7 +4375,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>国际关系学院</t>
+          <t>国防委员会</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -4363,7 +4387,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>习近平对俄罗斯、坦桑尼亚、南非、刚果共和国进行国事访问，并出席在南非举行的金砖国家领导人第五次会晤</t>
+          <t>一届全国人大一次会议举行</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4378,7 +4402,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>地方法院</t>
+          <t>国防科技大学</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -4390,7 +4414,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>中共中央办公厅、国务院办公厅印发《关于深化司法体制和社会体制改革的意见》</t>
+          <t>由中国人民解放军国防科技大学研制成功的中国第一台亿次巨型计算机——“银河-Ⅰ”计算机在长沙通过国家鉴定，填补了国内巨型计算机研制的空白</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4405,24 +4429,24 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>大兵团</t>
+          <t>国际关系学院</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>根据国民党军调集五十万兵力采取“分进合击”的战略方针向中央革命根据地发起第四次“围剿”的情况，周恩来、朱德指挥红一方面军先后在黄陂、草台冈、东陂等地区重创国民党“围剿”军，取得了粉碎第四次“围剿”的重大胜利</t>
+          <t>习近平对俄罗斯、坦桑尼亚、南非、刚果共和国进行国事访问，并出席在南非举行的金砖国家领导人第五次会晤</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434815/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -4432,24 +4456,24 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>小学教师</t>
+          <t>地方法院</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>邓小平在同方毅、胡乔木等谈全国教育工作会议的报告时提出，学校要整顿，要多招一些学生，要开辟新的发展领域和行业</t>
+          <t>中共中央办公厅、国务院办公厅印发《关于深化司法体制和社会体制改革的意见》</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434739/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -4459,7 +4483,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>工农红军</t>
+          <t>大兵团</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -4471,12 +4495,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>毛泽东率部打破江西国民党军队对井冈山地区的进攻</t>
+          <t>根据国民党军调集五十万兵力采取“分进合击”的战略方针向中央革命根据地发起第四次“围剿”的情况，周恩来、朱德指挥红一方面军先后在黄陂、草台冈、东陂等地区重创国民党“围剿”军，取得了粉碎第四次“围剿”的重大胜利</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434815/index.html</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -4486,24 +4510,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>工农联盟</t>
+          <t>小学教师</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>中国共产党第四次全国代表大会在上海举行</t>
+          <t>邓小平在同方毅、胡乔木等谈全国教育工作会议的报告时提出，学校要整顿，要多招一些学生，要开辟新的发展领域和行业</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434739/index.html</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -4513,24 +4537,24 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>巴黎公社</t>
+          <t>工农红军</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>毛泽东在广州国民党政治讲习班纪念巴黎公社五十五周年集会上发表讲演，着重总结了巴黎公社失败的教训</t>
+          <t>毛泽东率部打破江西国民党军队对井冈山地区的进攻</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434775/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -4540,24 +4564,24 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>延安大学</t>
+          <t>工农联盟</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>毛泽东在延安大学开学典礼上讲话</t>
+          <t>中国共产党第四次全国代表大会在上海举行</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434719/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -4567,7 +4591,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>总体布局</t>
+          <t>巴黎公社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -4579,12 +4603,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>《习近平关于实现中华民族伟大复兴的中国梦论述摘编》出版发行</t>
+          <t>毛泽东在广州国民党政治讲习班纪念巴黎公社五十五周年集会上发表讲演，着重总结了巴黎公社失败的教训</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434775/index.html</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -4594,7 +4618,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>总参谋部</t>
+          <t>延安大学</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -4606,12 +4630,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>新疆军区遵照军委总参谋部8月6日的批复公布成立新疆军区生产建设兵团</t>
+          <t>毛泽东在延安大学开学典礼上讲话</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434719/index.html</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -4621,19 +4645,19 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>总司令部</t>
+          <t>总体布局</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>中国工农红军总司令部成立，朱德任中国工农红军总司令，周恩来任总政治委员</t>
+          <t>《习近平关于实现中华民族伟大复兴的中国梦论述摘编》出版发行</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -4648,7 +4672,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>总后勤部</t>
+          <t>总参谋部</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -4660,7 +4684,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>解放军总参谋部、总政治部、总后勤部发出通知，规定预备役部队正式列入人民解放军建制序列</t>
+          <t>新疆军区遵照军委总参谋部8月6日的批复公布成立新疆军区生产建设兵团</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -4675,24 +4699,24 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>总工会</t>
+          <t>总司令部</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>京汉铁路工人两万余人举行总罢工，全路一千二百公里顿时瘫痪</t>
+          <t>中国工农红军总司令部成立，朱德任中国工农红军总司令，周恩来任总政治委员</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -4702,7 +4726,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>总指挥部</t>
+          <t>总后勤部</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -4714,7 +4738,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>中共中央革命军事委员会发布命令，宣布红军改名为国民革命军第八路军(简称八路军)，下辖三个师，全军约4.6万人</t>
+          <t>解放军总参谋部、总政治部、总后勤部发出通知，规定预备役部队正式列入人民解放军建制序列</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -4729,24 +4753,24 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>总政治部</t>
+          <t>总工会</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>解放军总参谋部、总政治部、总后勤部发出通知，规定预备役部队正式列入人民解放军建制序列</t>
+          <t>京汉铁路工人两万余人举行总罢工，全路一千二百公里顿时瘫痪</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -4756,24 +4780,24 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>我党我军</t>
+          <t>总指挥部</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>邓小平在北京病逝，享年93岁</t>
+          <t>中共中央革命军事委员会发布命令，宣布红军改名为国民革命军第八路军(简称八路军)，下辖三个师，全军约4.6万人</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434807/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -4783,24 +4807,24 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>战略部署</t>
+          <t>总政治部</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>中共中央发出《关于加强农村思想政治工作的通知》</t>
+          <t>解放军总参谋部、总政治部、总后勤部发出通知，规定预备役部队正式列入人民解放军建制序列</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434837/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -4810,24 +4834,24 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>抗日军政大学</t>
+          <t>我党我军</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>毛泽东为中国人民抗日军政大学第二期第二队学员题词：“要学习朱总司令：度量大如海，意志坚如钢</t>
+          <t>邓小平在北京病逝，享年93岁</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434759/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434807/index.html</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -4837,7 +4861,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>抗日红军大学</t>
+          <t>战略部署</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -4849,12 +4873,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>中国人民抗日军事政治大学(简称“抗大”)举行第二期开学典礼</t>
+          <t>中共中央发出《关于加强农村思想政治工作的通知》</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434838/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434837/index.html</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -4864,7 +4888,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>政协全国委员会</t>
+          <t>抗日军政大学</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -4876,12 +4900,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>政协全国委员会第49次常务委员会扩大会议在北京举行</t>
+          <t>毛泽东为中国人民抗日军政大学第二期第二队学员题词：“要学习朱总司令：度量大如海，意志坚如钢</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434470/434581/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434759/index.html</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -4891,24 +4915,24 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>新疆军区</t>
+          <t>抗日红军大学</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>新疆军区遵照军委总参谋部8月6日的批复公布成立新疆军区生产建设兵团</t>
+          <t>中国人民抗日军事政治大学(简称“抗大”)举行第二期开学典礼</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434838/index.html</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -4918,24 +4942,24 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团</t>
+          <t>政协全国委员会</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>新疆军区遵照军委总参谋部8月6日的批复公布成立新疆军区生产建设兵团</t>
+          <t>政协全国委员会第49次常务委员会扩大会议在北京举行</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434470/434581/index.html</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -4945,24 +4969,24 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>日本公明党</t>
+          <t>新疆军区</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>邓小平会见日本公明党委员长竹入义胜率领的日本公明党第八次访华团时，就中国的民主与法制建设问题指出：民主和法制，这两个方面都应该加强</t>
+          <t>新疆军区遵照军委总参谋部8月6日的批复公布成立新疆军区生产建设兵团</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434693/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -4972,24 +4996,24 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>日本共产党</t>
+          <t>新疆生产建设兵团</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>政党</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>毛泽东在会见日本共产党中央政治局委员听涛克己时，再次谈到两个中间地带问题</t>
+          <t>新疆军区遵照军委总参谋部8月6日的批复公布成立新疆军区生产建设兵团</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434822/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -4999,24 +5023,24 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>晋察冀军区</t>
+          <t>日本公明党</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>为适应解放战争胜利发展的形势，毛泽东、周恩来、任弼时率党中央领导机关自陕北米脂县杨家沟出发东渡黄河，与叶剑英、杨尚昆率领的中央后委会合</t>
+          <t>邓小平会见日本公明党委员长竹入义胜率领的日本公明党第八次访华团时，就中国的民主与法制建设问题指出：民主和法制，这两个方面都应该加强</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434778/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434693/index.html</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -5026,24 +5050,24 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>最高人民检察院</t>
+          <t>日本共产党</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>政党</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>中央政治局常委会召开会议，专门听取全国人大常委会、国务院、全国政协、最高人民法院、最高人民检察院党组工作汇报</t>
+          <t>毛泽东在会见日本共产党中央政治局委员听涛克己时，再次谈到两个中间地带问题</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434822/index.html</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -5053,24 +5077,24 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>最高人民法院</t>
+          <t>晋察冀军区</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>中央政治局常委会召开会议，专门听取全国人大常委会、国务院、全国政协、最高人民法院、最高人民检察院党组工作汇报</t>
+          <t>为适应解放战争胜利发展的形势，毛泽东、周恩来、任弼时率党中央领导机关自陕北米脂县杨家沟出发东渡黄河，与叶剑英、杨尚昆率领的中央后委会合</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434464/434778/index.html</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -5080,7 +5104,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>有限公司</t>
+          <t>最高人民检察院</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -5092,12 +5116,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司挂牌成立，至此，持续5年多的国有商业银行股份制改革基本完成</t>
+          <t>中央政治局常委会召开会议，专门听取全国人大常委会、国务院、全国政协、最高人民法院、最高人民检察院党组工作汇报</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -5107,7 +5131,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>服务大局</t>
+          <t>最高人民法院</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -5119,12 +5143,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>习近平指出，过去的一年是党和国家历史上很不平凡的一年</t>
+          <t>中央政治局常委会召开会议，专门听取全国人大常委会、国务院、全国政协、最高人民法院、最高人民检察院党组工作汇报</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -5134,24 +5158,24 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>朝鲜人民军</t>
+          <t>有限公司</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>朝鲜人民军来到志愿军阵地上，互相祝贺、共同欢呼抗美斗争的伟大胜利</t>
+          <t>中国农业银行股份有限公司挂牌成立，至此，持续5年多的国有商业银行股份制改革基本完成</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434662/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -5161,7 +5185,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>朝鲜劳动党</t>
+          <t>服务大局</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -5173,12 +5197,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>习近平对朝鲜民主主义人民共和国进行国事访问</t>
+          <t>习近平指出，过去的一年是党和国家历史上很不平凡的一年</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434792/index.html</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -5188,24 +5212,24 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>武装集团</t>
+          <t>朝鲜人民军</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>他强调，我军是执行党的政治任务的武装集团，军队党的建设必须高标准、严要求，努力走在全党前列</t>
+          <t>朝鲜人民军来到志愿军阵地上，互相祝贺、共同欢呼抗美斗争的伟大胜利</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434472/434483/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434662/index.html</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -5215,7 +5239,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>海关总署</t>
+          <t>朝鲜劳动党</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -5227,7 +5251,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>中央人民政府海关总署成立</t>
+          <t>习近平对朝鲜民主主义人民共和国进行国事访问</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -5242,24 +5266,24 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>海峡两岸关系协会</t>
+          <t>武装集团</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>海峡两岸关系协会与台湾海峡交流基金会，就解决两岸事务性商谈中如何表述坚持一个中国原则的问题，达成“海峡两岸同属一个中国，共同努力谋求国家统一”的共识，后被称为“九二共识”</t>
+          <t>他强调，我军是执行党的政治任务的武装集团，军队党的建设必须高标准、严要求，努力走在全党前列</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434472/434483/index.html</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -5269,7 +5293,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>海关总署</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -5281,12 +5305,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1991年4月22日 江泽民在四川考察工作时提出，要重视科学技术在现代战争中的作用</t>
+          <t>中央人民政府海关总署成立</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434748/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -5296,24 +5320,24 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>澳门特别行政区政府</t>
+          <t>海峡两岸关系协会</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>群团</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>本日，中华苏维埃中央政府及中共中央联名向南京、西安当局发出通电，重申和平解决西安事变的主张，并提出具体建议：双方军队暂以潼关为界，听候和平会议解决</t>
+          <t>海峡两岸关系协会与台湾海峡交流基金会，就解决两岸事务性商谈中如何表述坚持一个中国原则的问题，达成“海峡两岸同属一个中国，共同努力谋求国家统一”的共识，后被称为“九二共识”</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434473/434997/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -5323,24 +5347,24 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>省军区</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>中共湘鄂川黔边临时省委、省军区在大庸(今张家界)成立(后迁至湖南永顺塔卧丁家院)，任弼时任省委书记兼省军区政治委员</t>
+          <t>1991年4月22日 江泽民在四川考察工作时提出，要重视科学技术在现代战争中的作用</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434472/434503/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434748/index.html</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5350,7 +5374,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>石油工业部</t>
+          <t>澳门特别行政区政府</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -5362,12 +5386,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>中共中央批转石油工业部党组《关于组织华北石油勘探会战的报告》</t>
+          <t>本日，中华苏维埃中央政府及中共中央联名向南京、西安当局发出通电，重申和平解决西安事变的主张，并提出具体建议：双方军队暂以潼关为界，听候和平会议解决</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434842/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434473/434997/index.html</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5377,24 +5401,24 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>研究部署</t>
+          <t>省军区</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>中央政治局常委会会议专题听取有关国际金融危机情况和应采取应对措施的汇报</t>
+          <t>中共湘鄂川黔边临时省委、省军区在大庸(今张家界)成立(后迁至湖南永顺塔卧丁家院)，任弼时任省委书记兼省军区政治委员</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434472/434503/index.html</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5404,7 +5428,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>科学院</t>
+          <t>石油工业部</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -5416,12 +5440,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>中国中医科学院研究员屠呦呦获得2015年诺贝尔生理学或医学奖</t>
+          <t>中共中央批转石油工业部党组《关于组织华北石油勘探会战的报告》</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434842/index.html</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5431,24 +5455,24 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>红三军团</t>
+          <t>研究部署</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>毛泽东、朱德分析南昌的敌情和四面临水的地势，改变原来中央要求攻占南昌的计划，决定红一军团西渡赣江，乘虚向南昌对岸前进，避免了强攻中心城市可能遭受的损失，以实际行动抵制了中央攻打中心城市的军事冒险主义</t>
+          <t>中央政治局常委会会议专题听取有关国际金融危机情况和应采取应对措施的汇报</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434658/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5458,19 +5482,19 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>红二军团</t>
+          <t>科学院</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>红六军团从湘赣革命根据地突围西征</t>
+          <t>中国中医科学院研究员屠呦呦获得2015年诺贝尔生理学或医学奖</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -5485,7 +5509,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>红五军团</t>
+          <t>红三军团</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -5497,12 +5521,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>由红一军团和红五军团组成的东路军攻占漳州，俘敌一千六百余人，缴枪二千余支、飞机两架及其他大量军用物资，并筹得大批经费</t>
+          <t>毛泽东、朱德分析南昌的敌情和四面临水的地势，改变原来中央要求攻占南昌的计划，决定红一军团西渡赣江，乘虚向南昌对岸前进，避免了强攻中心城市可能遭受的损失，以实际行动抵制了中央攻打中心城市的军事冒险主义</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434746/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434468/434658/index.html</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -5512,7 +5536,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>红六军团</t>
+          <t>红二军团</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -5524,7 +5548,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>中旬　红军第六军团组建</t>
+          <t>红六军团从湘赣革命根据地突围西征</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -5539,24 +5563,24 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>红军前敌总指挥部</t>
+          <t>红五军团</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>中共中央革命军事委员会发布命令，宣布红军改名为国民革命军第八路军(简称八路军)，下辖三个师，全军约4.6万人</t>
+          <t>由红一军团和红五军团组成的东路军攻占漳州，俘敌一千六百余人，缴枪二千余支、飞机两架及其他大量军用物资，并筹得大批经费</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434465/434746/index.html</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -5566,24 +5590,24 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>红军大学</t>
+          <t>红六军团</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>中共中央政治局召开常委会议，讨论建立红军大学问题</t>
+          <t>中旬　红军第六军团组建</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434715/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -5593,7 +5617,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>纽约联合国总部</t>
+          <t>红军前敌总指挥部</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -5605,7 +5629,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>习近平对美国进行国事访问并出席联合国成立70周年系列峰会</t>
+          <t>中共中央革命军事委员会发布命令，宣布红军改名为国民革命军第八路军(简称八路军)，下辖三个师，全军约4.6万人</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -5620,7 +5644,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>经济布局</t>
+          <t>红军大学</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -5632,12 +5656,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>国家批准实施《广西北部湾经济区发展规划》，这是党中央、国务院深入全面实施西部大开发战略、完善区域经济布局、促进全国区域协调发展和开放合作而作出的重大决策</t>
+          <t>中共中央政治局召开常委会议，讨论建立红军大学问题</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434466/434715/index.html</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -5647,7 +5671,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>统治集团</t>
+          <t>纽约联合国总部</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -5659,12 +5683,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>晋冀鲁豫军区集中主力3万余人，在山西长治地区(古称上党郡)实施的上党战役，一举歼灭入侵的阎锡山所部3万余人，击毙国民党军第七集团军副总司令彭毓斌，生俘第十九军军长史泽波，使阎锡山损失其总兵力的1/3</t>
+          <t>习近平对美国进行国事访问并出席联合国成立70周年系列峰会</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434470/434583/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -5674,7 +5698,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>美国众议院</t>
+          <t>经济布局</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -5686,12 +5710,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>邓小平在会见美国众议院银行、财政和城市事务委员会访华团时，就中美关系指出：我们欢迎美国政治家们，同时也欢迎包括不赞成中美建交在内的美国人士都来中国看看，以增进两国和两国人民之间的了解</t>
+          <t>国家批准实施《广西北部湾经济区发展规划》，这是党中央、国务院深入全面实施西部大开发战略、完善区域经济布局、促进全国区域协调发展和开放合作而作出的重大决策</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434819/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434833/index.html</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5701,7 +5725,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>美国国务院</t>
+          <t>统治集团</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -5713,12 +5737,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>毛泽东以中共中央主席名义发表《反对美国对蒋军事援助法案的声明》</t>
+          <t>晋冀鲁豫军区集中主力3万余人，在山西长治地区(古称上党郡)实施的上党战役，一举歼灭入侵的阎锡山所部3万余人，击毙国民党军第七集团军副总司令彭毓斌，生俘第十九军军长史泽波，使阎锡山损失其总兵力的1/3</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434687/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434470/434583/index.html</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -5728,7 +5752,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>美国政府</t>
+          <t>美国众议院</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -5740,12 +5764,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>3月以来，针对美国政府单方面挑起的中美经贸摩擦，中国不得不采取中止关税减让义务、加征关税等反制措施，并在相互尊重、平等互利的原则基础上进行协商，坚决捍卫国家和人民利益</t>
+          <t>邓小平在会见美国众议院银行、财政和城市事务委员会访华团时，就中美关系指出：我们欢迎美国政治家们，同时也欢迎包括不赞成中美建交在内的美国人士都来中国看看，以增进两国和两国人民之间的了解</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434819/index.html</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5755,24 +5779,24 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>美国民主党</t>
+          <t>美国国务院</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>政党</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>邓小平会见以美国民主党众议员托马斯·路·阿什利为团长的美国众议院银行、财政和城市事务委员会访华团</t>
+          <t>毛泽东以中共中央主席名义发表《反对美国对蒋军事援助法案的声明》</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434819/index.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434467/434687/index.html</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -5782,7 +5806,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>联合政府</t>
+          <t>美国政府</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -5794,7 +5818,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>中共代表林伯渠在国民参政会上提出立即结束国民党一党统治、建立各抗日党派民主联合政府的主张</t>
+          <t>3月以来，针对美国政府单方面挑起的中美经贸摩擦，中国不得不采取中止关税减让义务、加征关税等反制措施，并在相互尊重、平等互利的原则基础上进行协商，坚决捍卫国家和人民利益</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -5809,24 +5833,24 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>苏区中央局</t>
+          <t>美国民主党</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>政党</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>中共中央成立南方局，重新成立北方局</t>
+          <t>邓小平会见以美国民主党众议员托马斯·路·阿什利为团长的美国众议院银行、财政和城市事务委员会访华团</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434819/index.html</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -5836,7 +5860,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>苏维埃政府</t>
+          <t>联合政府</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -5848,7 +5872,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>中共广东省委书记张太雷和叶挺、叶剑英等领导发动广州起义，成立广州苏维埃政府</t>
+          <t>中共代表林伯渠在国民参政会上提出立即结束国民党一党统治、建立各抗日党派民主联合政府的主张</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -5863,7 +5887,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>苏联政府</t>
+          <t>苏区中央局</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -5875,7 +5899,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>苏联政府决定同新中国建立外交关系</t>
+          <t>中共中央成立南方局，重新成立北方局</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -5890,24 +5914,24 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>苏联红军</t>
+          <t>苏维埃政府</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>毛泽东就庆祝苏联红军成立二十五周年与红军反攻的伟大胜利，致电斯大林、联共中央和红军将士们</t>
+          <t>中共广东省委书记张太雷和叶挺、叶剑英等领导发动广州起义，成立广州苏维埃政府</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434809/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -5917,7 +5941,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>葡萄牙共和国政府</t>
+          <t>苏联政府</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -5929,7 +5953,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>中葡两国政府在北京正式签署《中华人民共和国政府和葡萄牙共和国政府关于澳门问题的联合声明》，确认中国政府于1999年12月20日对澳门恢复行使主权</t>
+          <t>苏联政府决定同新中国建立外交关系</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -5944,24 +5968,24 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>财政经济委员会</t>
+          <t>苏联红军</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>中央人民政府海关总署成立</t>
+          <t>毛泽东就庆祝苏联红军成立二十五周年与红军反攻的伟大胜利，致电斯大林、联共中央和红军将士们</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434463/434809/index.html</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -5971,7 +5995,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>财经委员会</t>
+          <t>葡萄牙共和国政府</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -5983,7 +6007,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>习近平在中央财经委员会第七次会议上讲话提出，要构建以国内大循环为主体、国内国际双循环相互促进的新发展格局</t>
+          <t>中葡两国政府在北京正式签署《中华人民共和国政府和葡萄牙共和国政府关于澳门问题的联合声明》，确认中国政府于1999年12月20日对澳门恢复行使主权</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -5998,7 +6022,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>钢铁公司</t>
+          <t>财政经济委员会</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -6010,7 +6034,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>鞍山钢铁公司三大工程——大型轧钢厂、无缝钢管厂、七号炼铁炉举行开工生产典礼</t>
+          <t>中央人民政府海关总署成立</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -6025,19 +6049,19 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>陆海空军</t>
+          <t>财经委员会</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>军队</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>为显示中国人民完全有决心、有办法、有能力维护祖国统一，震慑“台独”势力，人民解放军向东海、南海进行发射导弹训练，并在东海、南海进行海空实弹演习和在台湾海峡进行陆海空军联合演习</t>
+          <t>习近平在中央财经委员会第七次会议上讲话提出，要构建以国内大循环为主体、国内国际双循环相互促进的新发展格局</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -6052,24 +6076,24 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>青年团</t>
+          <t>钢铁公司</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>群团</t>
+          <t>机构</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>广东海丰县农会成立</t>
+          <t>鞍山钢铁公司三大工程——大型轧钢厂、无缝钢管厂、七号炼铁炉举行开工生产典礼</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434818/index.html</t>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -6079,27 +6103,81 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>香港特别行政区基本法起草委员会</t>
+          <t>陆海空军</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>机构</t>
+          <t>军队</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
+          <t>为显示中国人民完全有决心、有办法、有能力维护祖国统一，震慑“台独”势力，人民解放军向东海、南海进行发射导弹训练，并在东海、南海进行海空实弹演习和在台湾海峡进行陆海空军联合演习</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>青年团</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>群团</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>广东海丰县农会成立</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/434462/434818/index.html</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>香港特别行政区基本法起草委员会</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
           <t>香港特别行政区基本法起草委员会第九次会议在北京举行</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>https://www.dswxyjy.org.cn/GB/434461/434463/434801/index.html</t>
         </is>
       </c>
-      <c r="G199" t="n">
+      <c r="G201" t="n">
         <v>0</v>
       </c>
     </row>
